--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="355">
   <si>
     <t>stream</t>
   </si>
@@ -1067,6 +1067,15 @@
   </si>
   <si>
     <t>jc, cs, plague</t>
+  </si>
+  <si>
+    <t>jc, cs lol</t>
+  </si>
+  <si>
+    <t>jc, marbels</t>
+  </si>
+  <si>
+    <t>jc, fgor</t>
   </si>
 </sst>
 </file>
@@ -13542,6 +13551,91 @@
         <v>10</v>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" s="1">
+        <v>716.0</v>
+      </c>
+      <c r="B718" s="1">
+        <v>1134.0</v>
+      </c>
+      <c r="C718" s="1">
+        <v>1308.0</v>
+      </c>
+      <c r="D718" s="1">
+        <v>139.0</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1">
+        <v>717.0</v>
+      </c>
+      <c r="B719" s="1">
+        <v>1277.0</v>
+      </c>
+      <c r="C719" s="1">
+        <v>1693.0</v>
+      </c>
+      <c r="D719" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1">
+        <v>718.0</v>
+      </c>
+      <c r="B720" s="1">
+        <v>974.0</v>
+      </c>
+      <c r="C720" s="1">
+        <v>1144.0</v>
+      </c>
+      <c r="D720" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1">
+        <v>719.0</v>
+      </c>
+      <c r="B721" s="1">
+        <v>1140.0</v>
+      </c>
+      <c r="C721" s="1">
+        <v>1331.0</v>
+      </c>
+      <c r="D721" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1">
+        <v>720.0</v>
+      </c>
+      <c r="B722" s="1">
+        <v>1529.0</v>
+      </c>
+      <c r="C722" s="1">
+        <v>1927.0</v>
+      </c>
+      <c r="D722" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="358">
   <si>
     <t>stream</t>
   </si>
@@ -1075,7 +1075,16 @@
     <t>jc, marbels</t>
   </si>
   <si>
-    <t>jc, fgor</t>
+    <t>jc, fhuor</t>
+  </si>
+  <si>
+    <t>jc, cs, fhuor</t>
+  </si>
+  <si>
+    <t>jc, tf2, cs</t>
+  </si>
+  <si>
+    <t>jc, tf2, fhuor2</t>
   </si>
 </sst>
 </file>
@@ -13636,6 +13645,91 @@
         <v>354</v>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" s="1">
+        <v>721.0</v>
+      </c>
+      <c r="B723" s="1">
+        <v>1044.0</v>
+      </c>
+      <c r="C723" s="1">
+        <v>1202.0</v>
+      </c>
+      <c r="D723" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1">
+        <v>722.0</v>
+      </c>
+      <c r="B724" s="1">
+        <v>1012.0</v>
+      </c>
+      <c r="C724" s="1">
+        <v>1221.0</v>
+      </c>
+      <c r="D724" s="1">
+        <v>113.0</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1">
+        <v>723.0</v>
+      </c>
+      <c r="B725" s="1">
+        <v>1155.0</v>
+      </c>
+      <c r="C725" s="1">
+        <v>2071.0</v>
+      </c>
+      <c r="D725" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1">
+        <v>724.0</v>
+      </c>
+      <c r="B726" s="1">
+        <v>1168.0</v>
+      </c>
+      <c r="C726" s="1">
+        <v>1600.0</v>
+      </c>
+      <c r="D726" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1">
+        <v>725.0</v>
+      </c>
+      <c r="B727" s="1">
+        <v>1194.0</v>
+      </c>
+      <c r="C727" s="1">
+        <v>1341.0</v>
+      </c>
+      <c r="D727" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="360">
   <si>
     <t>stream</t>
   </si>
@@ -1085,6 +1085,12 @@
   </si>
   <si>
     <t>jc, tf2, fhuor2</t>
+  </si>
+  <si>
+    <t>jc, bramble</t>
+  </si>
+  <si>
+    <t>jc, re6</t>
   </si>
 </sst>
 </file>
@@ -13730,6 +13736,74 @@
         <v>357</v>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" s="1">
+        <v>726.0</v>
+      </c>
+      <c r="B728" s="1">
+        <v>874.0</v>
+      </c>
+      <c r="C728" s="1">
+        <v>1143.0</v>
+      </c>
+      <c r="D728" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1">
+        <v>727.0</v>
+      </c>
+      <c r="B729" s="1">
+        <v>900.0</v>
+      </c>
+      <c r="C729" s="1">
+        <v>1023.0</v>
+      </c>
+      <c r="D729" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1">
+        <v>728.0</v>
+      </c>
+      <c r="B730" s="1">
+        <v>881.0</v>
+      </c>
+      <c r="C730" s="1">
+        <v>1081.0</v>
+      </c>
+      <c r="D730" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1">
+        <v>729.0</v>
+      </c>
+      <c r="B731" s="1">
+        <v>1104.0</v>
+      </c>
+      <c r="C731" s="1">
+        <v>1525.0</v>
+      </c>
+      <c r="D731" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="361">
   <si>
     <t>stream</t>
   </si>
@@ -1091,6 +1091,9 @@
   </si>
   <si>
     <t>jc, re6</t>
+  </si>
+  <si>
+    <t>jc, cs, hitman</t>
   </si>
 </sst>
 </file>
@@ -13804,6 +13807,57 @@
         <v>359</v>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" s="1">
+        <v>730.0</v>
+      </c>
+      <c r="B732" s="1">
+        <v>949.0</v>
+      </c>
+      <c r="C732" s="1">
+        <v>1151.0</v>
+      </c>
+      <c r="D732" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1">
+        <v>731.0</v>
+      </c>
+      <c r="B733" s="1">
+        <v>1120.0</v>
+      </c>
+      <c r="C733" s="1">
+        <v>1437.0</v>
+      </c>
+      <c r="D733" s="1">
+        <v>116.0</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1">
+        <v>732.0</v>
+      </c>
+      <c r="B734" s="1">
+        <v>1064.0</v>
+      </c>
+      <c r="C734" s="1">
+        <v>1244.0</v>
+      </c>
+      <c r="D734" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="361">
   <si>
     <t>stream</t>
   </si>
@@ -13858,6 +13858,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" s="1">
+        <v>733.0</v>
+      </c>
+      <c r="B735" s="1">
+        <v>1101.0</v>
+      </c>
+      <c r="C735" s="1">
+        <v>1636.0</v>
+      </c>
+      <c r="D735" s="1">
+        <v>128.0</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="362">
   <si>
     <t>stream</t>
   </si>
@@ -1094,6 +1094,9 @@
   </si>
   <si>
     <t>jc, cs, hitman</t>
+  </si>
+  <si>
+    <t>jc, devour</t>
   </si>
 </sst>
 </file>
@@ -13846,7 +13849,7 @@
         <v>732.0</v>
       </c>
       <c r="B734" s="1">
-        <v>1064.0</v>
+        <v>1071.0</v>
       </c>
       <c r="C734" s="1">
         <v>1244.0</v>
@@ -13863,7 +13866,7 @@
         <v>733.0</v>
       </c>
       <c r="B735" s="1">
-        <v>1101.0</v>
+        <v>1099.0</v>
       </c>
       <c r="C735" s="1">
         <v>1636.0</v>
@@ -13873,6 +13876,23 @@
       </c>
       <c r="E735" s="1" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1">
+        <v>734.0</v>
+      </c>
+      <c r="B736" s="1">
+        <v>1047.0</v>
+      </c>
+      <c r="C736" s="1">
+        <v>1245.0</v>
+      </c>
+      <c r="D736" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="363">
   <si>
     <t>stream</t>
   </si>
@@ -1097,6 +1097,9 @@
   </si>
   <si>
     <t>jc, devour</t>
+  </si>
+  <si>
+    <t>jc, lis</t>
   </si>
 </sst>
 </file>
@@ -13895,6 +13898,57 @@
         <v>361</v>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" s="1">
+        <v>735.0</v>
+      </c>
+      <c r="B737" s="1">
+        <v>1210.0</v>
+      </c>
+      <c r="C737" s="1">
+        <v>1527.0</v>
+      </c>
+      <c r="D737" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1">
+        <v>736.0</v>
+      </c>
+      <c r="B738" s="1">
+        <v>929.0</v>
+      </c>
+      <c r="C738" s="1">
+        <v>1153.0</v>
+      </c>
+      <c r="D738" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1">
+        <v>737.0</v>
+      </c>
+      <c r="B739" s="1">
+        <v>1033.0</v>
+      </c>
+      <c r="C739" s="1">
+        <v>1188.0</v>
+      </c>
+      <c r="D739" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="364">
   <si>
     <t>stream</t>
   </si>
@@ -1100,6 +1100,9 @@
   </si>
   <si>
     <t>jc, lis</t>
+  </si>
+  <si>
+    <t>jc, re6, outlastT</t>
   </si>
 </sst>
 </file>
@@ -13949,6 +13952,23 @@
         <v>362</v>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" s="1">
+        <v>738.0</v>
+      </c>
+      <c r="B740" s="1">
+        <v>834.0</v>
+      </c>
+      <c r="C740" s="1">
+        <v>1049.0</v>
+      </c>
+      <c r="D740" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="364">
   <si>
     <t>stream</t>
   </si>
@@ -13969,6 +13969,23 @@
         <v>363</v>
       </c>
     </row>
+    <row r="741">
+      <c r="A741" s="1">
+        <v>739.0</v>
+      </c>
+      <c r="B741" s="1">
+        <v>926.0</v>
+      </c>
+      <c r="C741" s="1">
+        <v>1094.0</v>
+      </c>
+      <c r="D741" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="365">
   <si>
     <t>stream</t>
   </si>
@@ -1103,6 +1103,9 @@
   </si>
   <si>
     <t>jc, re6, outlastT</t>
+  </si>
+  <si>
+    <t>jc, cs, dreadflats</t>
   </si>
 </sst>
 </file>
@@ -13986,6 +13989,40 @@
         <v>362</v>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="1">
+        <v>740.0</v>
+      </c>
+      <c r="B742" s="1">
+        <v>913.0</v>
+      </c>
+      <c r="C742" s="1">
+        <v>1117.0</v>
+      </c>
+      <c r="D742" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1">
+        <v>741.0</v>
+      </c>
+      <c r="B743" s="1">
+        <v>1041.0</v>
+      </c>
+      <c r="C743" s="1">
+        <v>1174.0</v>
+      </c>
+      <c r="D743" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="365">
   <si>
     <t>stream</t>
   </si>
@@ -14023,6 +14023,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" s="1">
+        <v>742.0</v>
+      </c>
+      <c r="B744" s="1">
+        <v>934.0</v>
+      </c>
+      <c r="C744" s="1">
+        <v>1109.0</v>
+      </c>
+      <c r="D744" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="365">
   <si>
     <t>stream</t>
   </si>
@@ -14040,6 +14040,23 @@
         <v>362</v>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" s="1">
+        <v>743.0</v>
+      </c>
+      <c r="B745" s="1">
+        <v>1013.0</v>
+      </c>
+      <c r="C745" s="1">
+        <v>1161.0</v>
+      </c>
+      <c r="D745" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="367">
   <si>
     <t>stream</t>
   </si>
@@ -1106,6 +1106,12 @@
   </si>
   <si>
     <t>jc, cs, dreadflats</t>
+  </si>
+  <si>
+    <t>jc, bloodwash</t>
+  </si>
+  <si>
+    <t>ic, outlastT</t>
   </si>
 </sst>
 </file>
@@ -14057,6 +14063,74 @@
         <v>10</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" s="1">
+        <v>744.0</v>
+      </c>
+      <c r="B746" s="1">
+        <v>910.0</v>
+      </c>
+      <c r="C746" s="1">
+        <v>1064.0</v>
+      </c>
+      <c r="D746" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1">
+        <v>745.0</v>
+      </c>
+      <c r="B747" s="1">
+        <v>1034.0</v>
+      </c>
+      <c r="C747" s="1">
+        <v>1689.0</v>
+      </c>
+      <c r="D747" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1">
+        <v>746.0</v>
+      </c>
+      <c r="B748" s="1">
+        <v>998.0</v>
+      </c>
+      <c r="C748" s="1">
+        <v>1138.0</v>
+      </c>
+      <c r="D748" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1">
+        <v>747.0</v>
+      </c>
+      <c r="B749" s="1">
+        <v>963.0</v>
+      </c>
+      <c r="C749" s="1">
+        <v>1162.0</v>
+      </c>
+      <c r="D749" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="368">
   <si>
     <t>stream</t>
   </si>
@@ -1112,6 +1112,9 @@
   </si>
   <si>
     <t>ic, outlastT</t>
+  </si>
+  <si>
+    <t>jc, cs, invokyr</t>
   </si>
 </sst>
 </file>
@@ -14131,6 +14134,23 @@
         <v>366</v>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" s="1">
+        <v>748.0</v>
+      </c>
+      <c r="B750" s="1">
+        <v>935.0</v>
+      </c>
+      <c r="C750" s="1">
+        <v>1062.0</v>
+      </c>
+      <c r="D750" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="370">
   <si>
     <t>stream</t>
   </si>
@@ -1115,6 +1115,12 @@
   </si>
   <si>
     <t>jc, cs, invokyr</t>
+  </si>
+  <si>
+    <t>jc, cs, hefollowedme</t>
+  </si>
+  <si>
+    <t>jc, obeythevoice</t>
   </si>
 </sst>
 </file>
@@ -14122,7 +14128,7 @@
         <v>747.0</v>
       </c>
       <c r="B749" s="1">
-        <v>963.0</v>
+        <v>947.0</v>
       </c>
       <c r="C749" s="1">
         <v>1162.0</v>
@@ -14139,7 +14145,7 @@
         <v>748.0</v>
       </c>
       <c r="B750" s="1">
-        <v>935.0</v>
+        <v>936.0</v>
       </c>
       <c r="C750" s="1">
         <v>1062.0</v>
@@ -14149,6 +14155,74 @@
       </c>
       <c r="E750" s="1" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1">
+        <v>749.0</v>
+      </c>
+      <c r="B751" s="1">
+        <v>946.0</v>
+      </c>
+      <c r="C751" s="1">
+        <v>1137.0</v>
+      </c>
+      <c r="D751" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1">
+        <v>750.0</v>
+      </c>
+      <c r="B752" s="1">
+        <v>856.0</v>
+      </c>
+      <c r="C752" s="1">
+        <v>1016.0</v>
+      </c>
+      <c r="D752" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1">
+        <v>751.0</v>
+      </c>
+      <c r="B753" s="1">
+        <v>820.0</v>
+      </c>
+      <c r="C753" s="1">
+        <v>993.0</v>
+      </c>
+      <c r="D753" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1">
+        <v>752.0</v>
+      </c>
+      <c r="B754" s="1">
+        <v>876.0</v>
+      </c>
+      <c r="C754" s="1">
+        <v>1161.0</v>
+      </c>
+      <c r="D754" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="371">
   <si>
     <t>stream</t>
   </si>
@@ -1121,6 +1121,9 @@
   </si>
   <si>
     <t>jc, obeythevoice</t>
+  </si>
+  <si>
+    <t>jc, cs, supernatural</t>
   </si>
 </sst>
 </file>
@@ -14225,6 +14228,23 @@
         <v>369</v>
       </c>
     </row>
+    <row r="755">
+      <c r="A755" s="1">
+        <v>753.0</v>
+      </c>
+      <c r="B755" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="C755" s="1">
+        <v>1429.0</v>
+      </c>
+      <c r="D755" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="372">
   <si>
     <t>stream</t>
   </si>
@@ -1124,6 +1124,9 @@
   </si>
   <si>
     <t>jc, cs, supernatural</t>
+  </si>
+  <si>
+    <t>jc, cs, skinfreak</t>
   </si>
 </sst>
 </file>
@@ -14245,6 +14248,23 @@
         <v>370</v>
       </c>
     </row>
+    <row r="756">
+      <c r="A756" s="1">
+        <v>754.0</v>
+      </c>
+      <c r="B756" s="1">
+        <v>1089.0</v>
+      </c>
+      <c r="C756" s="1">
+        <v>2054.0</v>
+      </c>
+      <c r="D756" s="1">
+        <v>-3.0</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="374">
   <si>
     <t>stream</t>
   </si>
@@ -1127,6 +1127,12 @@
   </si>
   <si>
     <t>jc, cs, skinfreak</t>
+  </si>
+  <si>
+    <t>jc, cs, remorses</t>
+  </si>
+  <si>
+    <t>jc, remorses</t>
   </si>
 </sst>
 </file>
@@ -14265,6 +14271,40 @@
         <v>371</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" s="1">
+        <v>755.0</v>
+      </c>
+      <c r="B757" s="1">
+        <v>1030.0</v>
+      </c>
+      <c r="C757" s="1">
+        <v>1211.0</v>
+      </c>
+      <c r="D757" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1">
+        <v>756.0</v>
+      </c>
+      <c r="B758" s="1">
+        <v>951.0</v>
+      </c>
+      <c r="C758" s="1">
+        <v>1476.0</v>
+      </c>
+      <c r="D758" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="374">
   <si>
     <t>stream</t>
   </si>
@@ -14305,6 +14305,23 @@
         <v>373</v>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="1">
+        <v>757.0</v>
+      </c>
+      <c r="B759" s="1">
+        <v>924.0</v>
+      </c>
+      <c r="C759" s="1">
+        <v>1086.0</v>
+      </c>
+      <c r="D759" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="374">
   <si>
     <t>stream</t>
   </si>
@@ -14322,6 +14322,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="760">
+      <c r="A760" s="1">
+        <v>758.0</v>
+      </c>
+      <c r="B760" s="1">
+        <v>1004.0</v>
+      </c>
+      <c r="C760" s="1">
+        <v>1267.0</v>
+      </c>
+      <c r="D760" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
